--- a/excel_template/Mastersheet_Template.xlsx
+++ b/excel_template/Mastersheet_Template.xlsx
@@ -10,6 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read Me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Company Info" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="News Feed" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Industry Data" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,10 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
+    <numFmt numFmtId="165" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,8 +62,16 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -70,6 +81,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001D4E4A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F8FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -119,6 +135,10 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -595,7 +615,7 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>This file ships pre-filled with sample historical data and a sample company profile as a worked example of the format. To reuse it for a real company: keep the sheet names and KPI row labels exactly as they are, replace the values in 'Monthly Data' with that company's numbers, and replace the placeholder values in 'Company Info' with their profile. No changes are needed on the dashboard's code side.</t>
+          <t>Keep the sheet names and KPI row labels exactly as they are, replace the values in 'Monthly Data' with the new company's numbers, replace the placeholder values in 'Company Info' with their profile, and replace (or delete) the illustrative example rows in 'News Feed' / 'Industry Data' with that company's own sourced research — or leave those two sheets empty until real research exists. No changes are needed on the dashboard's code side.</t>
         </is>
       </c>
     </row>
@@ -608,6 +628,18 @@
       <c r="B15" s="9" t="inlineStr">
         <is>
           <t>2021-03 through 2026-06 (64 months) of sample data. Treat the KPI values in this copy as illustrative placeholders, not a real company's actuals — replace them with your own company's numbers before using the dashboard for real reporting.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>The 'News Feed' and 'Industry Data' sheets (optional, Phase 2)</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Two more optional sheets power the News &amp; Updates and Industry &amp; Competitors sections. Both are shown here with clearly-labeled illustrative example rows only ('e.g. ...') — replace them with your own company's real, sourced research before uploading, or delete the example rows entirely to leave the sections showing their empty state. 'News Feed' is one row per news item (Title, Summary, Category, Published Date, Source Name, Source URL, Source Tier, Secondary Source Name/URL, Tags). 'Industry Data' is a long/tidy Section | Item | Field | Value table covering the industry overview, snapshot metrics, trends, competitor comparison and dashboard analysis. Both are independent of the financial 'Monthly Data' pipeline — a missing or malformed sheet here never affects the Performance section. Every item needs a real, working source URL; never invent one.</t>
         </is>
       </c>
     </row>
@@ -3046,4 +3078,942 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Summary</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Published Date</t>
+        </is>
+      </c>
+      <c r="E1" s="11" t="inlineStr">
+        <is>
+          <t>Source Name</t>
+        </is>
+      </c>
+      <c r="F1" s="11" t="inlineStr">
+        <is>
+          <t>Source URL</t>
+        </is>
+      </c>
+      <c r="G1" s="11" t="inlineStr">
+        <is>
+          <t>Source Tier</t>
+        </is>
+      </c>
+      <c r="H1" s="11" t="inlineStr">
+        <is>
+          <t>Secondary Source Name</t>
+        </is>
+      </c>
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>Secondary Source URL</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>Tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>e.g. Your Company launches [Product Name]</t>
+        </is>
+      </c>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>One or two sentences summarizing what happened and why it matters, based only on what your source actually says.</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Product &amp; Launches</t>
+        </is>
+      </c>
+      <c r="D2" s="13" t="n">
+        <v>46023</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Your Company (official)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://example.com/press-release</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Reuters (example)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://example.com/corroborating-article</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>example, replace me</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="n"/>
+      <c r="B3" s="9" t="n"/>
+      <c r="D3" s="13" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="B4" s="9" t="n"/>
+      <c r="D4" s="13" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="D5" s="13" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="D6" s="13" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="B1" s="11" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="C1" s="11" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="D1" s="11" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Overview</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>One paragraph describing what industry/category your company operates in, sourced from your own official materials.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Snapshot</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Metric 1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>e.g. Market Size</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Snapshot</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Metric 1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>e.g. $X Bn</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Snapshot</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Metric 1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Period</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>e.g. 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Snapshot</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Metric 1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>SourceName</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>e.g. Gartner</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Snapshot</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Metric 1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>SourceUrl</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>https://example.com/report</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Snapshot</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Metric 1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SourceTier</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Trend 1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Title</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>e.g. Name of the trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Trend 1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>What the trend is, in a sentence or two.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Trend 1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>WhyItMatters</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Why it's relevant to your company specifically.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Trend 1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>SourceName</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>e.g. McKinsey</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Trend 1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>SourceUrl</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>https://example.com/trend-report</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PrimaryFocus</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>e.g. What they primarily sell</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CRM</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Loyalty</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CDP</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>MarketingAutomation</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ConversationalCommerce</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Geography</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>e.g. Global</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>RelevanceNote</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>Why they're a real, evidenced competitor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>SourceName</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Example Competitor Inc.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SourceUrl</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>https://example.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Analysis 1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>Differentiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Analysis</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Analysis 1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>An interpretive statement clearly grounded in the sourced facts above — label it as analysis, not fact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Methodology</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>Explain how competitors/metrics here were selected and verified, so readers can judge the sourcing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="D27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="D28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="D29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="D30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="D31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="D32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="D33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="D35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="D36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="D37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="D38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="D39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="D40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="D41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="D42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="D43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="D44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="D45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="D46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="D47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="D48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="D49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="D50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="D51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="D52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="D53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="D54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="D55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="D56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="D57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="D58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="D59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="D60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="D61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="D62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="D63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="D64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="D65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="D66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="D67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="D68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="D69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="D70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="D71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="D72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="D73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="D74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="D75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="D76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="D77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="D78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="D79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="D80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="D81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="D82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="D83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="D84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="D85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="D86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="D87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="D88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="D89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="D90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="D91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="D92" s="9" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/excel_template/Mastersheet_Template.xlsx
+++ b/excel_template/Mastersheet_Template.xlsx
@@ -607,6 +607,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -619,6 +620,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -631,6 +633,7 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
